--- a/backend/测试数据/计算机网络期中考试测试数据.xlsx
+++ b/backend/测试数据/计算机网络期中考试测试数据.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\abc\xiaoxueqi_3\ai-teaching-evaluation-system-dev\backend\测试数据\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="21750" windowHeight="12040" activeTab="2"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="软件1801" sheetId="5" r:id="rId1"/>
@@ -1817,8 +1822,8 @@
         <v>28</v>
       </c>
       <c r="R2" s="8">
-        <f>100-J2-L2-N2-P2</f>
-        <v>92</v>
+        <f>100-H2-J2-L2-N2-P2</f>
+        <v>90</v>
       </c>
       <c r="S2" s="9"/>
       <c r="U2" s="19" t="s">
@@ -1878,8 +1883,8 @@
         <v>35</v>
       </c>
       <c r="R3" s="8">
-        <f t="shared" ref="R3:R26" si="0">100-J3-L3-N3-P3</f>
-        <v>87</v>
+        <f t="shared" ref="R3:R26" si="0">100-H3-J3-L3-N3-P3</f>
+        <v>84</v>
       </c>
       <c r="S3" s="9"/>
       <c r="U3" s="19" t="s">
@@ -1940,7 +1945,7 @@
       </c>
       <c r="R4" s="8">
         <f t="shared" si="0"/>
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S4" s="9"/>
       <c r="U4" s="19" t="s">
@@ -2001,7 +2006,7 @@
       </c>
       <c r="R5" s="8">
         <f t="shared" si="0"/>
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S5" s="9"/>
       <c r="U5" s="19" t="s">
@@ -2062,7 +2067,7 @@
       </c>
       <c r="R6" s="8">
         <f t="shared" si="0"/>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="S6" s="9"/>
       <c r="U6" s="19" t="s">
@@ -2123,7 +2128,7 @@
       </c>
       <c r="R7" s="8">
         <f t="shared" si="0"/>
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S7" s="9"/>
       <c r="U7" s="19" t="s">
@@ -2184,7 +2189,7 @@
       </c>
       <c r="R8" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S8" s="9"/>
       <c r="U8" s="19" t="s">
@@ -2245,7 +2250,7 @@
       </c>
       <c r="R9" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S9" s="9"/>
       <c r="U9" s="19" t="s">
@@ -2306,7 +2311,7 @@
       </c>
       <c r="R10" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S10" s="9"/>
       <c r="U10" s="19" t="s">
@@ -2367,7 +2372,7 @@
       </c>
       <c r="R11" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S11" s="9"/>
       <c r="U11" s="19" t="s">
@@ -2428,7 +2433,7 @@
       </c>
       <c r="R12" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S12" s="9"/>
     </row>
@@ -2486,7 +2491,7 @@
       </c>
       <c r="R13" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S13" s="9"/>
       <c r="U13" s="19" t="s">
@@ -2547,7 +2552,7 @@
       </c>
       <c r="R14" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S14" s="9"/>
       <c r="U14" s="19" t="s">
@@ -2608,7 +2613,7 @@
       </c>
       <c r="R15" s="8">
         <f t="shared" si="0"/>
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="S15" s="9"/>
       <c r="U15" s="19" t="s">
@@ -2669,7 +2674,7 @@
       </c>
       <c r="R16" s="8">
         <f t="shared" si="0"/>
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S16" s="9"/>
       <c r="U16" s="19" t="s">
@@ -2730,7 +2735,7 @@
       </c>
       <c r="R17" s="8">
         <f t="shared" si="0"/>
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="S17" s="9"/>
       <c r="U17" s="19" t="s">
@@ -2791,7 +2796,7 @@
       </c>
       <c r="R18" s="8">
         <f t="shared" si="0"/>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="S18" s="9"/>
       <c r="U18" s="19" t="s">
@@ -2852,7 +2857,7 @@
       </c>
       <c r="R19" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S19" s="9"/>
       <c r="U19" s="19" t="s">
@@ -2913,7 +2918,7 @@
       </c>
       <c r="R20" s="8">
         <f t="shared" si="0"/>
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S20" s="9"/>
       <c r="U20" s="19" t="s">
@@ -2974,7 +2979,7 @@
       </c>
       <c r="R21" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S21" s="9"/>
     </row>
@@ -3032,7 +3037,7 @@
       </c>
       <c r="R22" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S22" s="9"/>
       <c r="U22" s="19" t="s">
@@ -3093,7 +3098,7 @@
       </c>
       <c r="R23" s="8">
         <f t="shared" si="0"/>
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S23" s="9"/>
       <c r="U23" s="19" t="s">
@@ -3154,7 +3159,7 @@
       </c>
       <c r="R24" s="8">
         <f t="shared" si="0"/>
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="S24" s="9"/>
       <c r="U24" s="19" t="s">
@@ -3215,7 +3220,7 @@
       </c>
       <c r="R25" s="8">
         <f t="shared" si="0"/>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="S25" s="9"/>
       <c r="U25" s="19" t="s">
@@ -3276,7 +3281,7 @@
       </c>
       <c r="R26" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S26" s="9"/>
     </row>
@@ -3478,8 +3483,8 @@
         <v>28</v>
       </c>
       <c r="R2" s="8">
-        <f t="shared" ref="R2:R26" si="0">100-J2-L2-N2-P2</f>
-        <v>92</v>
+        <f>100-H2-J2-L2-N2-P2</f>
+        <v>90</v>
       </c>
       <c r="S2" s="9"/>
       <c r="T2" s="10"/>
@@ -3540,8 +3545,8 @@
         <v>35</v>
       </c>
       <c r="R3" s="8">
-        <f t="shared" si="0"/>
-        <v>87</v>
+        <f t="shared" ref="R3:R22" si="0">100-H3-J3-L3-N3-P3</f>
+        <v>84</v>
       </c>
       <c r="S3" s="9"/>
       <c r="T3" s="10"/>
@@ -3603,7 +3608,7 @@
       </c>
       <c r="R4" s="8">
         <f t="shared" si="0"/>
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S4" s="9"/>
       <c r="T4" s="10"/>
@@ -3665,7 +3670,7 @@
       </c>
       <c r="R5" s="8">
         <f t="shared" si="0"/>
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S5" s="9"/>
       <c r="T5" s="10"/>
@@ -3727,7 +3732,7 @@
       </c>
       <c r="R6" s="8">
         <f t="shared" si="0"/>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="S6" s="9"/>
       <c r="T6" s="10"/>
@@ -3789,7 +3794,7 @@
       </c>
       <c r="R7" s="8">
         <f t="shared" si="0"/>
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S7" s="9"/>
       <c r="T7" s="10"/>
@@ -3851,7 +3856,7 @@
       </c>
       <c r="R8" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S8" s="9"/>
       <c r="T8" s="10"/>
@@ -3913,7 +3918,7 @@
       </c>
       <c r="R9" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S9" s="9"/>
       <c r="T9" s="10"/>
@@ -3975,7 +3980,7 @@
       </c>
       <c r="R10" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S10" s="9"/>
       <c r="T10" s="10"/>
@@ -4037,7 +4042,7 @@
       </c>
       <c r="R11" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S11" s="9"/>
       <c r="T11" s="10"/>
@@ -4099,7 +4104,7 @@
       </c>
       <c r="R12" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S12" s="9"/>
     </row>
@@ -4157,7 +4162,7 @@
       </c>
       <c r="R13" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S13" s="9"/>
       <c r="T13" s="10"/>
@@ -4219,7 +4224,7 @@
       </c>
       <c r="R14" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S14" s="9"/>
       <c r="T14" s="10"/>
@@ -4281,7 +4286,7 @@
       </c>
       <c r="R15" s="8">
         <f t="shared" si="0"/>
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="S15" s="9"/>
       <c r="T15" s="10"/>
@@ -4343,7 +4348,7 @@
       </c>
       <c r="R16" s="8">
         <f t="shared" si="0"/>
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S16" s="9"/>
       <c r="T16" s="10"/>
@@ -4405,7 +4410,7 @@
       </c>
       <c r="R17" s="8">
         <f t="shared" si="0"/>
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="S17" s="9"/>
       <c r="T17" s="10"/>
@@ -4467,7 +4472,7 @@
       </c>
       <c r="R18" s="8">
         <f t="shared" si="0"/>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="S18" s="9"/>
       <c r="T18" s="10"/>
@@ -4529,7 +4534,7 @@
       </c>
       <c r="R19" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S19" s="9"/>
       <c r="T19" s="10"/>
@@ -4591,7 +4596,7 @@
       </c>
       <c r="R20" s="8">
         <f t="shared" si="0"/>
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S20" s="9"/>
       <c r="T20" s="10"/>
@@ -4653,7 +4658,7 @@
       </c>
       <c r="R21" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S21" s="9"/>
     </row>
@@ -4711,7 +4716,7 @@
       </c>
       <c r="R22" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S22" s="9"/>
       <c r="T22" s="10"/>
@@ -5071,8 +5076,8 @@
         <v>28</v>
       </c>
       <c r="R2" s="8">
-        <f t="shared" ref="R2:R26" si="0">100-J2-L2-N2-P2</f>
-        <v>92</v>
+        <f>100-H2-J2-L2-N2-P2</f>
+        <v>90</v>
       </c>
       <c r="S2" s="9"/>
       <c r="T2" s="10"/>
@@ -5133,8 +5138,8 @@
         <v>35</v>
       </c>
       <c r="R3" s="8">
-        <f t="shared" si="0"/>
-        <v>87</v>
+        <f t="shared" ref="R3:R23" si="0">100-H3-J3-L3-N3-P3</f>
+        <v>84</v>
       </c>
       <c r="S3" s="9"/>
       <c r="T3" s="10"/>
@@ -5196,7 +5201,7 @@
       </c>
       <c r="R4" s="8">
         <f t="shared" si="0"/>
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S4" s="9"/>
       <c r="T4" s="10"/>
@@ -5258,7 +5263,7 @@
       </c>
       <c r="R5" s="8">
         <f t="shared" si="0"/>
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S5" s="9"/>
       <c r="T5" s="10"/>
@@ -5320,7 +5325,7 @@
       </c>
       <c r="R6" s="8">
         <f t="shared" si="0"/>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="S6" s="9"/>
       <c r="T6" s="10"/>
@@ -5382,7 +5387,7 @@
       </c>
       <c r="R7" s="8">
         <f t="shared" si="0"/>
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S7" s="9"/>
       <c r="T7" s="10"/>
@@ -5444,7 +5449,7 @@
       </c>
       <c r="R8" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S8" s="9"/>
       <c r="T8" s="10"/>
@@ -5506,7 +5511,7 @@
       </c>
       <c r="R9" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S9" s="9"/>
       <c r="T9" s="10"/>
@@ -5568,7 +5573,7 @@
       </c>
       <c r="R10" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S10" s="9"/>
       <c r="T10" s="10"/>
@@ -5630,7 +5635,7 @@
       </c>
       <c r="R11" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S11" s="9"/>
       <c r="T11" s="10"/>
@@ -5692,7 +5697,7 @@
       </c>
       <c r="R12" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S12" s="9"/>
       <c r="T12" s="10"/>
@@ -5752,7 +5757,7 @@
       </c>
       <c r="R13" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S13" s="9"/>
       <c r="T13" s="10"/>
@@ -5814,7 +5819,7 @@
       </c>
       <c r="R14" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S14" s="9"/>
       <c r="T14" s="10"/>
@@ -5876,7 +5881,7 @@
       </c>
       <c r="R15" s="8">
         <f t="shared" si="0"/>
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="S15" s="9"/>
       <c r="T15" s="10"/>
@@ -5938,7 +5943,7 @@
       </c>
       <c r="R16" s="8">
         <f t="shared" si="0"/>
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S16" s="9"/>
       <c r="T16" s="10"/>
@@ -6000,7 +6005,7 @@
       </c>
       <c r="R17" s="8">
         <f t="shared" si="0"/>
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="S17" s="9"/>
       <c r="T17" s="10"/>
@@ -6062,7 +6067,7 @@
       </c>
       <c r="R18" s="8">
         <f t="shared" si="0"/>
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="S18" s="9"/>
       <c r="T18" s="10"/>
@@ -6124,7 +6129,7 @@
       </c>
       <c r="R19" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S19" s="9"/>
       <c r="T19" s="10"/>
@@ -6186,7 +6191,7 @@
       </c>
       <c r="R20" s="8">
         <f t="shared" si="0"/>
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S20" s="9"/>
       <c r="T20" s="10"/>
@@ -6248,7 +6253,7 @@
       </c>
       <c r="R21" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S21" s="9"/>
       <c r="T21" s="10"/>
@@ -6308,7 +6313,7 @@
       </c>
       <c r="R22" s="8">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S22" s="9"/>
       <c r="T22" s="10"/>
@@ -6370,7 +6375,7 @@
       </c>
       <c r="R23" s="8">
         <f t="shared" si="0"/>
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="S23" s="9"/>
       <c r="T23" s="10"/>
